--- a/AAII_Financials/Quarterly/ET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>ET</t>
   </si>
@@ -656,506 +656,518 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34334000</v>
+      </c>
+      <c r="E8" s="3">
         <v>27771000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25320000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19954000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19242000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21020000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19541000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20772000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20729000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21629000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20532000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20739000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18320000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18995000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20501000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22939000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>25945000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20491000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18657000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16664000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15101000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16995000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10034000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9955000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7338000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11627000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13720000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13495000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>26998000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13121000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13573000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14514000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>26000000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>11882000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11451000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>9984000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9427000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9661000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28764000</v>
+      </c>
+      <c r="E9" s="3">
         <v>22844000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20876000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16094000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15289000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16870000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15438000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16970000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16836000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17735000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16800000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17164000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15186000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15635000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16063000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18516000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21515000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16138000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14754000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13188000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>11505000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10909000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6703000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6376000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4117000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8408000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20179000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19723000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>30121000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9470000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10204000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>11117000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>20264000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9194000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8991000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7313000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7205000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>7519000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5570000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4927000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4444000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3860000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3953000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4150000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4103000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3802000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3893000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3894000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3732000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3575000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3134000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3360000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4438000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4423000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4430000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4353000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3903000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3476000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3596000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6086000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3331000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3579000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3221000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3219000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-6459000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-6228000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-3123000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3651000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3369000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3397000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5736000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2688000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2460000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2671000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2222000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2142000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1196,8 +1208,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1312,8 +1325,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1428,240 +1444,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>7000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>280000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>20000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-542000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>626000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>86000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>9000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>90000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1474000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1387000</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>12000</v>
       </c>
       <c r="AD14" s="3">
         <v>12000</v>
       </c>
       <c r="AE14" s="3">
-        <v>68000</v>
+        <v>12000</v>
       </c>
       <c r="AF14" s="3">
         <v>68000</v>
       </c>
       <c r="AG14" s="3">
+        <v>68000</v>
+      </c>
+      <c r="AH14" s="3">
         <v>437000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <v>106000</v>
       </c>
       <c r="AK14" s="3">
+        <v>106000</v>
+      </c>
+      <c r="AL14" s="3">
         <v>1004000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>89000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1575000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1583000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1491000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1440000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1384000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1367000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1374000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1324000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1213000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1254000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1158000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1107000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1061000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1059000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1060000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1030000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1046000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1028000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>980000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>943000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>940000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>954000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>963000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>912000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>936000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>867000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1608000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1568000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2344000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1548000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>750000</v>
       </c>
       <c r="AH15" s="3">
         <v>750000</v>
       </c>
       <c r="AI15" s="3">
+        <v>750000</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>1359000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>665000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>677000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>642000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>607000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>628000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1699,240 +1724,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30760000</v>
+      </c>
+      <c r="E17" s="3">
         <v>24788000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22967000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17802000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16930000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18525000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17260000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18591000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18381000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19249000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18367000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18505000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16475000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16932000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18695000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20966000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23832000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18645000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16998000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15227000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13505000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12933000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8708000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9711000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6002000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11628000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12058000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>11639000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>23331000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>11274000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12160000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12811000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>23880000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10888000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11225000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9053000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8684000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8929000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3574000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2983000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2353000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2152000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2312000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2495000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2281000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2181000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2348000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2380000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2165000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2234000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1845000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2063000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1806000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1973000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2113000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1846000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1659000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1437000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1596000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4062000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1326000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>244000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1336000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1662000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1856000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3667000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1847000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1413000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1703000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2120000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>994000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>226000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>931000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>743000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>732000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1973,588 +2005,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-82000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-218000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-130000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-110000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-81000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-130000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-176000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-88000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-125000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-99000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-148000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-112000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-95000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>268000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>173000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>191000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>76000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>105000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-40000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>243000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>153000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>14000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-333000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>798000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>543000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>566000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>173000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>299000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>188000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-333000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>143000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>81000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>109000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5233000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4648000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4062000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3722000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3806000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3943000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3785000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3681000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3649000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3759000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3422000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3489000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3018000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3217000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3134000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3011000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3332000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3065000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2715000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2485000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2496000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5259000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2442000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1121000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>2286000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>533000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3264000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3183000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5792000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2608000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2144000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2626000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3778000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1847000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>570000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1716000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1431000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1469000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>934000</v>
+      </c>
+      <c r="E22" s="3">
         <v>947000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>910000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>890000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>865000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>809000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>813000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>834000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>759000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>719000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>650000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>632000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>641000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>639000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>592000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>577000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>578000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>559000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>554000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>558000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>566000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>589000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>577000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>569000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>579000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>602000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1168000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1158000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>1746000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>590000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>544000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>535000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>976000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>466000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>482000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>490000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>477000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>473000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2724000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2111000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1381000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1379000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1537000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1761000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1583000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1523000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2219000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1781000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1614000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1124000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1341000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1518000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1482000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1404000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1708000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1478000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1181000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>984000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>990000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3716000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>902000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-360000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>771000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-936000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1292000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1241000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2487000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1244000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>850000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1341000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1443000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>716000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-589000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>584000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>347000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>368000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E24" s="3">
         <v>135000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>143000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>87000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>79000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>136000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>89000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>227000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>89000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>47000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>77000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>108000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>71000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>45000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>82000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>86000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-9000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-50000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>77000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>82000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>75000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>69000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>41000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>99000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>160000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>126000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-52000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>58000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-10000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>65000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-157000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>33000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2669,240 +2717,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2530000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1976000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1238000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1292000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1458000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1720000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1447000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1434000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1992000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1692000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1567000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1047000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1233000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1447000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1437000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1322000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1622000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1487000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1231000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>907000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>908000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3641000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>833000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-401000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>672000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-964000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1311000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1187000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2327000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1118000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>852000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1393000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1385000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>726000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-654000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>741000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>314000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>330000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2027000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1194000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>868000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>959000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1091000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1255000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1008000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1115000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1182000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1089000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1203000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>466000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>797000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1003000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1049000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>899000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1220000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1162000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>820000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>535000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>539000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3285000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>636000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-655000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>353000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-854000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>972000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>857000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1685000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>807000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>617000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>372000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>934000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>578000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1583000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>223000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>397000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>243000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3017,8 +3074,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3094,12 +3154,12 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -3113,28 +3173,31 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-263000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-237000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>1822000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>17000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-193000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3249,8 +3312,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3365,240 +3431,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E32" s="3">
         <v>82000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>218000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>130000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>110000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>81000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>130000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>176000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>88000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>125000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>99000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>148000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>112000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>95000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-268000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-173000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-191000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-76000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-105000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>40000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-243000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-153000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>35000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>333000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-798000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-543000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-566000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>13000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>19000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-173000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-299000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-188000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>333000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-143000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-81000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-109000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2086000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1253000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>927000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1018000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1162000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1322000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1076000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1182000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1313000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1239000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1326000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>584000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>910000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1112000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1049000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>899000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1220000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1162000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>820000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>535000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>539000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3285000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>636000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-655000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>353000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-854000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>972000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>857000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1685000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>807000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>617000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>370000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>341000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>239000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>240000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>204000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3713,245 +3788,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2086000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1253000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>927000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1018000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1162000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1322000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1076000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1182000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1313000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1239000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1326000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>584000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>910000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1112000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1049000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>899000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1220000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1162000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>820000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>535000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>539000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3285000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>636000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-655000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>353000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-854000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>972000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>857000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1685000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>807000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>617000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>370000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>341000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>239000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>240000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>204000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3992,8 +4076,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4034,124 +4119,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1020000</v>
+      </c>
+      <c r="E41" s="3">
         <v>951000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1272000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3574000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>242000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>453000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>312000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>299000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>650000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1946000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>161000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>514000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>330000</v>
       </c>
       <c r="P41" s="3">
         <v>330000</v>
       </c>
       <c r="Q41" s="3">
+        <v>330000</v>
+      </c>
+      <c r="R41" s="3">
         <v>257000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>326000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>353000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1111000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>336000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>313000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>282000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>355000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>367000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>275000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>155000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>196000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>291000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>211000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>445000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>529000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>419000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>398000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>519000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>547000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>336000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>469000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>375000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>370000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4266,820 +4355,844 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17069000</v>
+      </c>
+      <c r="E43" s="3">
         <v>15890000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11451000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10040000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10103000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11524000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10334000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10034000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9680000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9820000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9215000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9797000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7465000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8441000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8627000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8744000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10371000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10103000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7740000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6542000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5976000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5407000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3989000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3898000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3163000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3618000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5343000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4643000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4559000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4479000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4193000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4657000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4587000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3849000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4693000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3641000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3465000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3557000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4385000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4645000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4770000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3269000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2795000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2787000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3070000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2502000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2624000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2267000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2478000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2590000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2271000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2047000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2461000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2490000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2216000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1981000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2014000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1811000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1664000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1810000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1739000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1723000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1593000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1024000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1532000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1814000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1832000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1722000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1677000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2066000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1802000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1861000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2022000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1957000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1882000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>639000</v>
+      </c>
+      <c r="E45" s="3">
         <v>777000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>268000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>559000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>531000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>473000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>159000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>501000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>452000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>985000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>271000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>522000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>532000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>552000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>736000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>599000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2494000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2504000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>447000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>383000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>286000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>248000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>222000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>254000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>245000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>281000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>573000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>398000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>362000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>397000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>461000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>406000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>685000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>336000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3632000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4622000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4604000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>522000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23113000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22263000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18233000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17442000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13671000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15237000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14202000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13336000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13406000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15018000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12433000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13423000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10598000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11370000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12081000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12159000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15434000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15699000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10537000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9049000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8208000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7820000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6317000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6150000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5156000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5119000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>7464000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>7066000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7198000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7127000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6750000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7527000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7593000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>6593000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>10683000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>10689000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>10326000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6514000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3637000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3646000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3589000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3269000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3243000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3260000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3266000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3268000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3236000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3093000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3097000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2993000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3007000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2861000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2893000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2869000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2924000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2921000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2947000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2958000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3025000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3009000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3060000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3068000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3311000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3337000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3460000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2992000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2838000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2653000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2642000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2656000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2687000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2701000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2705000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3177000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>3182000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>3103000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106035000</v>
+      </c>
+      <c r="E48" s="3">
         <v>105985000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>103983000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>96909000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>96359000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>96068000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>96021000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>95848000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>92742000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>85906000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>86177000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>81693000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>81975000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>80817000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>81130000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>81076000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>80690000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>80865000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>82445000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>75100000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>75392000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>75661000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>75973000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>76062000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>76053000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>75619000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>75157000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>70058000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>69040000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>68189000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>66963000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>65643000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>64880000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>61975000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>61088000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>59267000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>56808000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>56967000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12768000</v>
+      </c>
+      <c r="E49" s="3">
         <v>12899000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12890000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9563000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9677000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9791000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9874000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10012000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10112000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9998000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10258000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7768000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7865000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7888000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7981000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8058000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8160000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8141000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8389000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7869000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7953000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8048000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8137000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8333000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9875000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9951000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11321000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10651000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10710000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10797000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10885000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>11255000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>11261000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>10704000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>10884000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>11356000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>11441000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>13587000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5194,8 +5307,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5310,124 +5426,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2615000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2689000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2445000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2148000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2072000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2069000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1866000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1965000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1843000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1774000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1585000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1694000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1687000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1585000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1558000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1573000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1561000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1566000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1645000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1722000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1664000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1680000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1657000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1582000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1512000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1515000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1571000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1089000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1026000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1007000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1106000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>996000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>936000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>886000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>891000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>852000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>826000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5542,124 +5664,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>148168000</v>
+      </c>
+      <c r="E54" s="3">
         <v>147482000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>141286000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>129331000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>125022000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>126425000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>125380000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>124429000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121339000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>115789000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>113698000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>107571000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>105132000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>104521000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>105643000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>105735000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>108769000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>109192000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>105963000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>96698000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96242000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>96218000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95144000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>95195000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>95907000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>95541000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>98973000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>91856000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>90812000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>89773000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>88246000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>88187000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>87417000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>82909000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>86246000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>85380000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>82609000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>80997000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5700,8 +5828,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5742,168 +5871,172 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13767000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13152000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9510000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7336000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7537000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8999000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8325000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7382000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7478000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7564000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6684000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8004000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6179000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6943000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6969000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7523000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8914000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8654000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6834000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5707000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5023000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4755000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2836000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2795000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2153000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2408000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4149000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3551000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3659000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4018000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3552000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4044000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4057000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3757000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4716000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4040000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3392000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3396000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>227000</v>
+      </c>
+      <c r="E58" s="3">
         <v>220000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>270000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>75000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>73000</v>
       </c>
       <c r="H58" s="3">
         <v>73000</v>
       </c>
       <c r="I58" s="3">
+        <v>73000</v>
+      </c>
+      <c r="J58" s="3">
         <v>75000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>328000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>323000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1236000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1064000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1051000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3504000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>47000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2000</v>
       </c>
       <c r="R58" s="3">
         <v>2000</v>
@@ -5912,534 +6045,549 @@
         <v>2000</v>
       </c>
       <c r="T58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U58" s="3">
         <v>652000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>681000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>678000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>674000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>23000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>21000</v>
       </c>
       <c r="Z58" s="3">
         <v>21000</v>
       </c>
       <c r="AA58" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AB58" s="3">
         <v>34000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>33000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>27000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>158000</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>2655000</v>
       </c>
       <c r="AH58" s="3">
         <v>2655000</v>
       </c>
       <c r="AI58" s="3">
+        <v>2655000</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>160000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>409000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>413000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>716000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1370000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>392000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>467000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2959000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2412000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>173000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1840000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>79000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>64000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3397000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3718000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4559000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4413000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3320000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3449000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2850000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3001000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3066000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3231000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2816000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3725000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6888000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3471000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2762000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2519000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3103000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3520000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3419000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3095000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2768000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3091000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3003000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2430000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19858000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19043000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14955000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12410000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11849000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13571000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12656000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12371000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11709000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12719000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11277000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12755000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13013000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10162000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10368000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11243000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13475000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13719000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10835000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9834000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8547000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7779000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5923000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6047000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5003000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6166000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7724000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7037000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6429000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6695000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9310000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10219000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7636000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7261000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7897000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7847000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>7765000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>6218000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>70014000</v>
+      </c>
+      <c r="E61" s="3">
         <v>70886000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69824000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>63899000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>61503000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>60534000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>60483000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59737000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58109000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52991000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>52158000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47850000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45458000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48020000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>48260000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47413000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>48104000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>48826000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49023000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>44793000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>45612000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>47712000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>51417000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>51424000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>51251000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>50299000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>51030000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>46842000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>46501000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>46375000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>43373000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>42117000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>44473000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>41779000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>43671000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>44495000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>43084000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>42583000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1946000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1973000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1940000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1615000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1609000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1561000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1617000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1613000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1631000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1604000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1615000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2016000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1365000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1417000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5863000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6018000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5932000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5825000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5977000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5939000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6032000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5704000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5654000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5677000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6011000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5801000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5542000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5436000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5365000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5142000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4214000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4319000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4438000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4367000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4677000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6377000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6549000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>6439000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6554,8 +6702,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6670,8 +6821,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6786,124 +6940,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>97390000</v>
+      </c>
+      <c r="E66" s="3">
         <v>97493000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92026000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>82187000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>79165000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>79845000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>78946000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77831000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>75450000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71323000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>68981000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>66512000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>63675000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63358000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72618000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>72904000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>76193000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>77188000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>74660000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>69285000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>68976000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>74781000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>76617000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>76931000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>76121000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>76132000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>77053000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>70938000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>69978000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>69119000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>67687000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>89290000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>88527000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>84089000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>87442000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>86572000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>83794000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>82144000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6944,8 +7104,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7060,8 +7221,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7176,94 +7340,97 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>3356000</v>
+      </c>
+      <c r="E70" s="3">
         <v>3388000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>3356000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>3388000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>3356000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>3892000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>3852000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>3892000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>3852000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>5626000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>6459000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>6083000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>6042000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>6080000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>6049000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>6074000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>6048000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>6074000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>6047000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>5666000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>5649000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>-5000</v>
-      </c>
-      <c r="Y70" s="3">
-        <v>-8000</v>
       </c>
       <c r="Z70" s="3">
         <v>-8000</v>
       </c>
       <c r="AA70" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="AB70" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>-6000</v>
-      </c>
-      <c r="AC70" s="3">
-        <v>-4000</v>
       </c>
       <c r="AD70" s="3">
         <v>-4000</v>
       </c>
       <c r="AE70" s="3">
-        <v>-5000</v>
+        <v>-4000</v>
       </c>
       <c r="AF70" s="3">
         <v>-5000</v>
@@ -7272,28 +7439,31 @@
         <v>-5000</v>
       </c>
       <c r="AH70" s="3">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="AI70" s="3">
         <v>-4000</v>
       </c>
       <c r="AJ70" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="AK70" s="3">
         <v>516000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>447000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>374000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>305000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>242000</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7408,8 +7578,11 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7452,8 +7625,8 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -7524,8 +7697,11 @@
       <c r="AN72" s="3">
         <v>0</v>
       </c>
+      <c r="AO72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7640,8 +7816,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7756,8 +7935,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7872,124 +8054,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31976000</v>
+      </c>
+      <c r="E76" s="3">
         <v>31076000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>31012000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31291000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31425000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31428000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31268000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>31350000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30462000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30309000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30225000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27043000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27511000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27070000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>26976000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>26757000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>26528000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>25930000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>25256000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21747000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21617000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21442000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>18535000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18272000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>19793000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>19415000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21924000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20922000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20839000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20659000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20564000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1099000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-1106000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-1696000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-1643000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-1566000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>-1389000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8104,245 +8292,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2086000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1253000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>927000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1018000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1162000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1322000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1076000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1182000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1313000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1239000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1326000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>584000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>910000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1112000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1049000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>899000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1220000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1162000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>820000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>535000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>539000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3285000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>636000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-655000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>353000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-854000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>972000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>857000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1685000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>807000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>617000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>370000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>341000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>239000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>240000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>204000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>232000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8383,124 +8580,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1384000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1367000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>910000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1324000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1213000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1254000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>759000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1107000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1061000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1059000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>670000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1030000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1046000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1060000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1030000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1046000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1028000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>980000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>943000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>940000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>954000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>963000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>912000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>936000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>867000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>804000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>784000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1559000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>774000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>750000</v>
       </c>
       <c r="AH83" s="3">
         <v>750000</v>
       </c>
       <c r="AI83" s="3">
+        <v>750000</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>1359000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>665000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>677000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>642000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>574000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>661000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8615,8 +8816,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8731,8 +8935,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8847,8 +9054,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8963,8 +9173,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9079,124 +9292,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4271000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3378000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1898000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2572000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2762000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2917000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2590000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2874000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2270000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3772000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1296000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2373000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2536000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3350000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1338000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2989000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2354000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2370000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1739000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2263000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2005000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5155000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1906000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2296000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1331000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1828000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2090000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2072000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3894000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1815000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2207000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2131000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2695000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1665000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1013000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1954000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>700000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>893000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9237,124 +9456,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1564000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1916000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1947000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1473000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1659000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1224000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1472000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1086000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-811000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-795000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-704000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-701000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-876000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-853000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-888000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1035000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-706000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-752000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-776000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-617000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-731000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-698000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1138000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1271000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1621000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1779000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1363000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2818000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1150000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2232000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1636000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3539000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-3232000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1462000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1408000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9469,8 +9692,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9585,124 +9811,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3946000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1528000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1701000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1198000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1469000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3284000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>45000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1196000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-964000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-670000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1888000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-803000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-945000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1123000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-683000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1271000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-868000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-578000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-694000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-635000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1037000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1098000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1206000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1557000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2511000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1481000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2942000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1098000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2312000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1626000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1513000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-802000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3243000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1803000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9743,124 +9975,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>1140000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1129000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>986000</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1105000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1081000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>827000</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1039000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>963000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>952000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>942000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>920000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-929000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-775000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-735000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-608000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-515000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-485000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-492000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-406000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-405000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-813000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-814000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-770000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>2300000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-751000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1549000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-800000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-798000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-354000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-532000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-266000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-258000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-251000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-250000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-251000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9975,8 +10211,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10091,8 +10330,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10207,124 +10449,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2602000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1165000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-254000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2288000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1578000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1108000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>59000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3611000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-791000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-685000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1519000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-648000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2474000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-462000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1893000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2429000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-324000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-848000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1654000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1384000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4532000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-777000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1102000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-154000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-354000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>554000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-825000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-607000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>126000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-626000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2582000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2967000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-350000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>1384000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>1128000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1209000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10367,8 +10615,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10439,120 +10687,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-321000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2302000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3332000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-211000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>141000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-351000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1296000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1785000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-353000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>184000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>73000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-69000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-27000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-758000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>775000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>31000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-73000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>92000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>120000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-95000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>80000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>26000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>110000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>21000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-121000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>183000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>211000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-139000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>96000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>25000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-113000</v>
       </c>
     </row>
